--- a/CO国試data/CO_questions_2018.xlsx
+++ b/CO国試data/CO_questions_2018.xlsx
@@ -542,15 +542,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -599,7 +599,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>False</t>
@@ -635,15 +634,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -692,7 +691,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>False</t>
@@ -728,15 +726,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>3</v>
       </c>
@@ -785,7 +783,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>True</t>
@@ -821,15 +818,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -878,7 +875,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>False</t>
@@ -914,15 +910,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>内分泌</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -971,7 +967,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>True</t>
@@ -1007,15 +1002,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>免疫機構</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1064,7 +1059,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>False</t>
@@ -1100,15 +1094,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1157,7 +1151,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>False</t>
@@ -1193,15 +1186,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>3</v>
       </c>
@@ -1250,7 +1243,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>False</t>
@@ -1286,15 +1278,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -1343,7 +1335,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>False</t>
@@ -1379,15 +1370,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>免疫機構</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -1436,7 +1427,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>False</t>
@@ -1472,15 +1462,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>4</v>
       </c>
@@ -1529,7 +1519,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>False</t>
@@ -1565,19 +1554,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>生理光学</t>
+          <t>基礎視能矯正学</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>3</v>
       </c>
@@ -1626,7 +1611,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>False</t>
@@ -1662,19 +1646,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>生理光学</t>
+          <t>基礎視能矯正学</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>3</v>
       </c>
@@ -1723,7 +1703,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>False</t>
@@ -1759,15 +1738,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>3</v>
       </c>
@@ -1816,7 +1795,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>False</t>
@@ -1852,15 +1830,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>3</v>
       </c>
@@ -1909,7 +1887,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>False</t>
@@ -1945,15 +1922,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -2002,7 +1979,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>False</t>
@@ -2038,15 +2014,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>3</v>
       </c>
@@ -2095,7 +2071,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>True</t>
@@ -2131,15 +2106,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -2188,7 +2163,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>False</t>
@@ -2224,15 +2198,15 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>4</v>
       </c>
@@ -2281,7 +2255,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>False</t>
@@ -2317,15 +2290,15 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>3</v>
       </c>
@@ -2374,7 +2347,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>False</t>
@@ -2413,12 +2385,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>1</v>
       </c>
@@ -2467,7 +2439,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>False</t>
@@ -2506,12 +2477,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>2</v>
       </c>
@@ -2560,7 +2531,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>False</t>
@@ -2599,12 +2569,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -2653,7 +2623,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>False</t>
@@ -2692,12 +2661,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>1</v>
       </c>
@@ -2746,7 +2715,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>False</t>
@@ -2782,15 +2750,15 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>3</v>
       </c>
@@ -2839,7 +2807,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>False</t>
@@ -2875,15 +2842,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>4</v>
       </c>
@@ -2973,15 +2940,15 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>3</v>
       </c>
@@ -3030,7 +2997,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>False</t>
@@ -3066,15 +3032,15 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>3</v>
       </c>
@@ -3124,7 +3090,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>False</t>
@@ -3160,15 +3125,15 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>3</v>
       </c>
@@ -3217,7 +3182,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>True</t>
@@ -3253,15 +3217,15 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>3</v>
       </c>
@@ -3310,7 +3274,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>True</t>
@@ -3346,15 +3309,15 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>3</v>
       </c>
@@ -3403,7 +3366,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>True</t>
@@ -3439,15 +3401,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>3</v>
       </c>
@@ -3496,7 +3458,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>False</t>
@@ -3532,15 +3493,15 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -3589,7 +3550,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>False</t>
@@ -3625,15 +3585,15 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>4</v>
       </c>
@@ -3683,7 +3643,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
           <t>False</t>
@@ -3719,15 +3678,15 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>3</v>
       </c>
@@ -3776,7 +3735,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>False</t>
@@ -3812,15 +3770,15 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>3</v>
       </c>
@@ -3869,7 +3827,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>False</t>
@@ -3905,15 +3862,15 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>3</v>
       </c>
@@ -3962,7 +3919,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>False</t>
@@ -3998,15 +3954,15 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4055,7 +4011,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
           <t>False</t>
@@ -4091,15 +4046,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>2</v>
       </c>
@@ -4148,7 +4103,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
           <t>False</t>
@@ -4184,15 +4138,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>3</v>
       </c>
@@ -4241,7 +4195,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>False</t>
@@ -4277,15 +4230,15 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>3</v>
       </c>
@@ -4334,7 +4287,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>False</t>
@@ -4370,15 +4322,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>2</v>
       </c>
@@ -4427,7 +4379,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>False</t>
@@ -4463,15 +4414,15 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>2</v>
       </c>
@@ -4520,7 +4471,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
           <t>False</t>
@@ -4556,15 +4506,15 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -4613,7 +4563,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
           <t>False</t>
@@ -4649,15 +4598,15 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>3</v>
       </c>
@@ -4706,7 +4655,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
           <t>False</t>
@@ -4742,15 +4690,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>3</v>
       </c>
@@ -4799,7 +4747,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
           <t>False</t>
@@ -4835,15 +4782,15 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>3</v>
       </c>
@@ -4892,7 +4839,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
           <t>True</t>
@@ -4931,12 +4877,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>2</v>
       </c>
@@ -4985,7 +4931,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>False</t>
@@ -5021,15 +4966,15 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>3</v>
       </c>
@@ -5078,7 +5023,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
           <t>False</t>
@@ -5114,15 +5058,15 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>2</v>
       </c>
@@ -5171,7 +5115,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
           <t>False</t>
@@ -5207,19 +5150,15 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
+          <t>視能訓練学</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>3</v>
       </c>
@@ -5268,7 +5207,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
           <t>True</t>
@@ -5307,12 +5245,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>1</v>
       </c>
@@ -5361,7 +5299,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
           <t>False</t>
@@ -5397,15 +5334,15 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>2</v>
       </c>
@@ -5454,7 +5391,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
           <t>False</t>
@@ -5490,15 +5426,15 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>3</v>
       </c>
@@ -5547,7 +5483,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
           <t>True</t>
@@ -5583,15 +5518,15 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>4</v>
       </c>
@@ -5640,7 +5575,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
           <t>False</t>
@@ -5676,15 +5610,15 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>4</v>
       </c>
@@ -5733,7 +5667,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
           <t>False</t>
@@ -5769,15 +5702,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>2</v>
       </c>
@@ -5826,7 +5759,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
           <t>False</t>
@@ -5862,15 +5794,15 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>3</v>
       </c>
@@ -5919,7 +5851,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
           <t>True</t>
@@ -5955,15 +5886,15 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>3</v>
       </c>
@@ -6012,7 +5943,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
           <t>False</t>
@@ -6048,15 +5978,15 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>3</v>
       </c>
@@ -6105,7 +6035,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
           <t>False</t>
@@ -6141,15 +6070,15 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>3</v>
       </c>
@@ -6198,7 +6127,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
           <t>False</t>
@@ -6234,15 +6162,15 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>2</v>
       </c>
@@ -6291,7 +6219,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
           <t>False</t>
@@ -6327,15 +6254,15 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>4</v>
       </c>
@@ -6425,15 +6352,15 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>2</v>
       </c>
@@ -6482,7 +6409,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
           <t>False</t>
@@ -6518,15 +6444,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>4</v>
       </c>
@@ -6575,7 +6501,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
           <t>True</t>
@@ -6611,15 +6536,15 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>5</v>
       </c>
@@ -6709,15 +6634,15 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>4</v>
       </c>
@@ -6806,15 +6731,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>3</v>
       </c>
@@ -6863,7 +6788,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
           <t>False</t>
@@ -6899,15 +6823,15 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>5</v>
       </c>
@@ -6997,15 +6921,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>4</v>
       </c>
@@ -7055,7 +6979,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
           <t>False</t>
@@ -7091,15 +7014,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>3</v>
       </c>
@@ -7189,15 +7112,15 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>4</v>
       </c>
@@ -7287,15 +7210,15 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>3</v>
       </c>
@@ -7345,7 +7268,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
           <t>False</t>
@@ -7381,15 +7303,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7439,7 +7361,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
           <t>False</t>
@@ -7475,15 +7396,15 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>3</v>
       </c>
@@ -7533,7 +7454,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
           <t>False</t>
@@ -7569,15 +7489,15 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>1</v>
       </c>
@@ -7626,7 +7546,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
           <t>False</t>
@@ -7662,15 +7581,15 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>個体の構造</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7719,7 +7638,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
           <t>False</t>
@@ -7755,15 +7673,15 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>3</v>
       </c>
@@ -7812,7 +7730,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
           <t>False</t>
@@ -7848,15 +7765,15 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>3</v>
       </c>
@@ -7905,7 +7822,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
           <t>False</t>
@@ -7941,15 +7857,15 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>1</v>
       </c>
@@ -7998,7 +7914,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
           <t>False</t>
@@ -8037,12 +7952,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>2</v>
       </c>
@@ -8091,7 +8006,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
           <t>False</t>
@@ -8127,15 +8041,15 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>2</v>
       </c>
@@ -8184,7 +8098,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
           <t>False</t>
@@ -8220,15 +8133,15 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>3</v>
       </c>
@@ -8277,7 +8190,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
           <t>True</t>
@@ -8316,12 +8228,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>2</v>
       </c>
@@ -8370,7 +8282,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
           <t>False</t>
@@ -8409,12 +8320,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>3</v>
       </c>
@@ -8463,7 +8374,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
           <t>False</t>
@@ -8499,15 +8409,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>2</v>
       </c>
@@ -8556,7 +8466,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
           <t>False</t>
@@ -8592,15 +8501,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>4</v>
       </c>
@@ -8649,7 +8558,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
           <t>True</t>
@@ -8685,15 +8593,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>3</v>
       </c>
@@ -8742,7 +8650,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
           <t>True</t>
@@ -8778,15 +8685,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>1</v>
       </c>
@@ -8835,7 +8742,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
           <t>False</t>
@@ -8871,15 +8777,15 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>4</v>
       </c>
@@ -8969,15 +8875,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>3</v>
       </c>
@@ -9026,7 +8932,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
           <t>False</t>
@@ -9062,15 +8967,15 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>2</v>
       </c>
@@ -9119,7 +9024,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
           <t>False</t>
@@ -9155,15 +9059,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>4</v>
       </c>
@@ -9213,7 +9117,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
           <t>True</t>
@@ -9249,15 +9152,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>3</v>
       </c>
@@ -9307,7 +9210,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
           <t>False</t>
@@ -9343,15 +9245,15 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>2</v>
       </c>
@@ -9400,7 +9302,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
           <t>False</t>
@@ -9439,12 +9340,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>視能障害のリハビリテーション</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>2</v>
       </c>
@@ -9495,7 +9396,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
           <t>False</t>
@@ -9531,15 +9431,15 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>2</v>
       </c>
@@ -9588,7 +9488,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
           <t>False</t>
@@ -9624,15 +9523,15 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>2</v>
       </c>
@@ -9681,7 +9580,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
           <t>False</t>
@@ -9717,15 +9615,15 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>3</v>
       </c>
@@ -9774,7 +9672,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
           <t>True</t>
@@ -9810,15 +9707,15 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>2</v>
       </c>
@@ -9867,7 +9764,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
           <t>False</t>
@@ -9903,15 +9799,15 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>2</v>
       </c>
@@ -9960,7 +9856,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
           <t>False</t>
@@ -9996,15 +9891,15 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>2</v>
       </c>
@@ -10053,7 +9948,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
           <t>False</t>
@@ -10089,15 +9983,15 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>2</v>
       </c>
@@ -10146,7 +10040,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
           <t>False</t>
@@ -10182,15 +10075,15 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>2</v>
       </c>
@@ -10239,7 +10132,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
           <t>False</t>
@@ -10275,15 +10167,15 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10332,7 +10224,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
           <t>False</t>
@@ -10368,15 +10259,15 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>3</v>
       </c>
@@ -10425,7 +10316,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
           <t>True</t>
@@ -10461,15 +10351,15 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>3</v>
       </c>
@@ -10519,7 +10409,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
           <t>False</t>
@@ -10555,15 +10444,15 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>3</v>
       </c>
@@ -10612,7 +10501,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
           <t>False</t>
@@ -10648,15 +10536,15 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>3</v>
       </c>
@@ -10706,7 +10594,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
           <t>True</t>
@@ -10742,15 +10629,15 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>3</v>
       </c>
@@ -10799,7 +10686,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
           <t>True</t>
@@ -10835,15 +10721,15 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>3</v>
       </c>
@@ -10877,7 +10763,6 @@
           <t>輻湊近点の限界を超えたとき複視を自覚しない。 -- 耳側網膜の抑制</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>図を参照。不備問題として採点除外。間欠性外斜視に関する問題。</t>
@@ -10888,7 +10773,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
           <t>True</t>
@@ -10924,15 +10808,15 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>3</v>
       </c>
@@ -11022,15 +10906,15 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>2</v>
       </c>
@@ -11079,7 +10963,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
           <t>False</t>
@@ -11115,19 +10998,15 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
+          <t>視能訓練学</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>1</v>
       </c>
@@ -11176,7 +11055,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
           <t>False</t>
@@ -11212,15 +11090,15 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11269,7 +11147,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
           <t>False</t>
@@ -11305,15 +11182,15 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>4</v>
       </c>
@@ -11362,7 +11239,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
           <t>False</t>
@@ -11398,15 +11274,15 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>4</v>
       </c>
@@ -11456,7 +11332,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
           <t>False</t>
@@ -11492,15 +11367,15 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>3</v>
       </c>
@@ -11549,7 +11424,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
           <t>False</t>
@@ -11585,15 +11459,15 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>2</v>
       </c>
@@ -11642,7 +11516,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
           <t>False</t>
@@ -11678,15 +11551,15 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>2</v>
       </c>
@@ -11735,7 +11608,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
           <t>False</t>
@@ -11771,15 +11643,15 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>3</v>
       </c>
@@ -11828,7 +11700,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
           <t>True</t>
@@ -11864,15 +11735,15 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>2</v>
       </c>
@@ -11921,7 +11792,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
           <t>False</t>
@@ -11957,15 +11827,15 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>3</v>
       </c>
@@ -12014,7 +11884,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
           <t>False</t>
@@ -12050,15 +11919,15 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>1</v>
       </c>
@@ -12107,7 +11976,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
           <t>False</t>
@@ -12143,15 +12011,15 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>4</v>
       </c>
@@ -12200,7 +12068,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
           <t>True</t>
@@ -12236,19 +12103,15 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
+          <t>視能訓練学</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>2</v>
       </c>
@@ -12297,7 +12160,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
           <t>False</t>
@@ -12333,15 +12195,15 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>2</v>
       </c>
@@ -12390,7 +12252,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
           <t>False</t>
@@ -12426,19 +12287,15 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
+          <t>視能訓練学</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>3</v>
       </c>
@@ -12487,7 +12344,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
           <t>False</t>
@@ -12523,15 +12379,15 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>3</v>
       </c>
@@ -12580,7 +12436,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
           <t>False</t>
@@ -12616,15 +12471,15 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>3</v>
       </c>
@@ -12673,7 +12528,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
           <t>False</t>
@@ -12709,15 +12563,15 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>2</v>
       </c>
@@ -12766,7 +12620,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
           <t>False</t>
@@ -12802,15 +12655,15 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>2</v>
       </c>
@@ -12859,7 +12712,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
           <t>False</t>
@@ -12895,15 +12747,15 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>2</v>
       </c>
@@ -12952,7 +12804,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
           <t>False</t>
@@ -12988,15 +12839,15 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>3</v>
       </c>
@@ -13046,7 +12897,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
           <t>False</t>
@@ -13082,15 +12932,15 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>2</v>
       </c>
@@ -13139,7 +12989,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
           <t>False</t>
@@ -13175,15 +13024,15 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>3</v>
       </c>
@@ -13273,15 +13122,15 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>3</v>
       </c>
@@ -13330,7 +13179,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
           <t>False</t>
@@ -13366,15 +13214,15 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>3</v>
       </c>
@@ -13424,7 +13272,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
           <t>False</t>
@@ -13460,15 +13307,15 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>3</v>
       </c>
@@ -13517,7 +13364,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
           <t>False</t>
@@ -13553,15 +13399,15 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>3</v>
       </c>
@@ -13610,7 +13456,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
           <t>False</t>
@@ -13646,15 +13491,15 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>4</v>
       </c>
@@ -13744,15 +13589,15 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
         <v>3</v>
       </c>
@@ -13802,7 +13647,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
           <t>False</t>
@@ -13838,15 +13682,15 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>4</v>
       </c>
@@ -13936,15 +13780,15 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>3</v>
       </c>
@@ -13994,7 +13838,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
           <t>False</t>
@@ -14030,15 +13873,15 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>3</v>
       </c>
@@ -14088,7 +13931,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
           <t>False</t>
@@ -14124,15 +13966,15 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>4</v>
       </c>
@@ -14222,15 +14064,15 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>4</v>
       </c>
@@ -14280,7 +14122,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr">
         <is>
           <t>True</t>
@@ -14316,15 +14157,15 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>4</v>
       </c>
@@ -14414,15 +14255,15 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
         <v>3</v>
       </c>
@@ -14472,7 +14313,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr">
         <is>
           <t>True</t>
@@ -14508,15 +14348,15 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
         <v>3</v>
       </c>
@@ -14566,7 +14406,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
           <t>False</t>

--- a/CO国試data/CO_questions_2018.xlsx
+++ b/CO国試data/CO_questions_2018.xlsx
@@ -542,12 +542,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>神経の構造と機能</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -634,12 +634,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -726,12 +726,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼球</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -818,12 +818,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -910,12 +910,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>内分泌</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>内分泌</t>
+          <t>内分泌器官の構造と機能</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>免疫機構</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>免疫機構</t>
+          <t>免疫系の構成・機能</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼球</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>免疫機構</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>免疫機構</t>
+          <t>免疫系の構成・機能</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1830,12 +1830,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2014,12 +2014,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2566,12 +2566,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2658,12 +2658,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -2842,12 +2842,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>網膜</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2940,12 +2940,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>涙液検査</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3217,12 +3217,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3309,12 +3309,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3493,12 +3493,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3585,12 +3585,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -3678,12 +3678,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3770,12 +3770,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3862,12 +3862,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>電気生理検査</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -3954,12 +3954,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>角膜</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4046,12 +4046,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>角膜</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4230,12 +4230,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼窩</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4414,12 +4414,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>ぶどう膜</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼瞼</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -4690,12 +4690,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼球運動</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -4782,12 +4782,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -4874,12 +4874,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>公衆衛生総論</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -4966,12 +4966,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5058,12 +5058,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5242,12 +5242,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -5334,12 +5334,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -5610,12 +5610,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -5702,12 +5702,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -5794,12 +5794,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -5886,12 +5886,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -5978,12 +5978,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6070,12 +6070,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -6254,12 +6254,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -6352,12 +6352,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -6536,12 +6536,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>電気生理検査</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -6731,12 +6731,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -6823,12 +6823,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>網膜</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -6921,12 +6921,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>角膜</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -7014,12 +7014,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -7112,12 +7112,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -7210,12 +7210,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -7303,12 +7303,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -7396,12 +7396,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>個体の構造</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>個体の構造</t>
+          <t>細胞の構造と機能</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -7673,12 +7673,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -7765,12 +7765,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -7949,12 +7949,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>公衆衛生総論</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -8133,12 +8133,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -8225,12 +8225,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -8409,12 +8409,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -8501,12 +8501,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>両眼視</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -8685,12 +8685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -8777,12 +8777,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -8875,12 +8875,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -8967,12 +8967,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>屈折異常</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -9059,12 +9059,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -9337,12 +9337,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能障害のリハビリテーション</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>視能障害のリハビリテーション</t>
+          <t>ロービジョン</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -9523,12 +9523,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -9615,12 +9615,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -9707,12 +9707,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -9799,12 +9799,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼球</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -9891,12 +9891,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -9983,12 +9983,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>瞳孔反応</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -10075,12 +10075,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -10167,12 +10167,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -10259,12 +10259,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -10351,12 +10351,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -10444,12 +10444,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>光学的視能矯正</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -10536,12 +10536,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -10721,12 +10721,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -10808,12 +10808,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>前眼部、透光体検査</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -10906,12 +10906,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>水晶体</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -10998,12 +10998,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -11090,12 +11090,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -11182,12 +11182,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -11274,12 +11274,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -11367,12 +11367,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -11459,12 +11459,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>全身疾患と眼</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -11551,12 +11551,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -11643,12 +11643,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -11735,12 +11735,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>網膜</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -11827,12 +11827,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>硝子体</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -12011,12 +12011,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -12103,12 +12103,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -12195,12 +12195,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -12287,12 +12287,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -12471,12 +12471,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -12563,12 +12563,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -12655,12 +12655,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -12747,12 +12747,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>両眼視</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -12839,12 +12839,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -12932,12 +12932,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -13024,12 +13024,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -13122,12 +13122,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -13214,12 +13214,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -13307,12 +13307,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -13399,12 +13399,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -13491,12 +13491,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼瞼</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -13682,12 +13682,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -13780,12 +13780,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -13966,12 +13966,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -14064,12 +14064,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -14255,12 +14255,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>光学的視能矯正</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -14348,12 +14348,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>

--- a/CO国試data/CO_questions_2018.xlsx
+++ b/CO国試data/CO_questions_2018.xlsx
@@ -550,7 +550,11 @@
           <t>神経の構造と機能</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>シナプス、神経伝達物質</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -642,7 +646,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>副交感神経薬</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -734,7 +742,11 @@
           <t>眼球</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>水晶体</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
@@ -826,7 +838,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -918,7 +929,11 @@
           <t>内分泌器官の構造と機能</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>副腎皮質</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -1010,7 +1025,6 @@
           <t>免疫系の構成・機能</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1102,7 +1116,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1194,7 +1207,6 @@
           <t>眼球</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>3</v>
       </c>
@@ -1286,7 +1298,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -1378,7 +1389,6 @@
           <t>免疫系の構成・機能</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -1470,7 +1480,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>4</v>
       </c>
@@ -1562,7 +1571,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>3</v>
       </c>
@@ -1654,7 +1662,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>3</v>
       </c>
@@ -1746,7 +1753,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>3</v>
       </c>
@@ -1838,7 +1849,6 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>3</v>
       </c>
@@ -1930,7 +1940,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -2022,7 +2031,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>眼鏡レンズ</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>3</v>
       </c>
@@ -2114,7 +2127,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -2206,7 +2218,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>乱視</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>4</v>
       </c>
@@ -2298,7 +2314,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>3</v>
       </c>
@@ -2390,7 +2410,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>1</v>
       </c>
@@ -2482,7 +2501,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>2</v>
       </c>
@@ -2574,7 +2592,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -2666,7 +2683,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>1</v>
       </c>
@@ -2758,7 +2774,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>乱視</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>3</v>
       </c>
@@ -2850,7 +2870,6 @@
           <t>網膜</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>4</v>
       </c>
@@ -2948,7 +2967,6 @@
           <t>涙液検査</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>3</v>
       </c>
@@ -3040,7 +3058,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>3</v>
       </c>
@@ -3133,7 +3155,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>3</v>
       </c>
@@ -3225,7 +3246,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>3</v>
       </c>
@@ -3317,7 +3337,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H32" t="n">
         <v>3</v>
       </c>
@@ -3409,7 +3433,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H33" t="n">
         <v>3</v>
       </c>
@@ -3501,7 +3529,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -3593,7 +3625,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>4</v>
       </c>
@@ -3686,7 +3717,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>3</v>
       </c>
@@ -3778,7 +3808,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>3</v>
       </c>
@@ -3870,7 +3899,11 @@
           <t>電気生理検査</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>網膜電図〈ERG〉</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>3</v>
       </c>
@@ -3962,7 +3995,11 @@
           <t>角膜</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>角膜変性（症）、角膜ジストロフィ</t>
+        </is>
+      </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4054,7 +4091,6 @@
           <t>角膜</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>2</v>
       </c>
@@ -4146,7 +4182,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>3</v>
       </c>
@@ -4238,7 +4273,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>3</v>
       </c>
@@ -4330,7 +4364,11 @@
           <t>眼窩</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>眼球突出、陥凹</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>2</v>
       </c>
@@ -4422,7 +4460,11 @@
           <t>ぶどう膜</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>虹彩毛様体炎</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>2</v>
       </c>
@@ -4514,7 +4556,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -4606,7 +4647,11 @@
           <t>眼瞼</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>眼瞼下垂</t>
+        </is>
+      </c>
       <c r="H46" t="n">
         <v>3</v>
       </c>
@@ -4698,7 +4743,11 @@
           <t>眼球運動</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>神経筋接合部障害</t>
+        </is>
+      </c>
       <c r="H47" t="n">
         <v>3</v>
       </c>
@@ -4790,7 +4839,6 @@
           <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>3</v>
       </c>
@@ -4882,7 +4930,6 @@
           <t>公衆衛生総論</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>2</v>
       </c>
@@ -4974,7 +5021,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H50" t="n">
         <v>3</v>
       </c>
@@ -5066,7 +5117,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H51" t="n">
         <v>2</v>
       </c>
@@ -5158,7 +5213,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>3</v>
       </c>
@@ -5250,7 +5304,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>1</v>
       </c>
@@ -5342,7 +5395,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>副交感神経薬</t>
+        </is>
+      </c>
       <c r="H54" t="n">
         <v>2</v>
       </c>
@@ -5434,7 +5491,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>3</v>
       </c>
@@ -5526,7 +5582,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>4</v>
       </c>
@@ -5618,7 +5673,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>共同筋と拮抗筋</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>4</v>
       </c>
@@ -5710,7 +5769,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>2</v>
       </c>
@@ -5802,7 +5860,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>3</v>
       </c>
@@ -5894,7 +5951,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>3</v>
       </c>
@@ -5986,7 +6042,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H61" t="n">
         <v>3</v>
       </c>
@@ -6078,7 +6138,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H62" t="n">
         <v>3</v>
       </c>
@@ -6170,7 +6234,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>2</v>
       </c>
@@ -6262,7 +6325,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>4</v>
       </c>
@@ -6360,7 +6422,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H65" t="n">
         <v>2</v>
       </c>
@@ -6452,7 +6518,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>4</v>
       </c>
@@ -6544,7 +6609,11 @@
           <t>電気生理検査</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>網膜電図〈ERG〉</t>
+        </is>
+      </c>
       <c r="H67" t="n">
         <v>5</v>
       </c>
@@ -6642,7 +6711,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>4</v>
       </c>
@@ -6739,7 +6807,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>3</v>
       </c>
@@ -6831,7 +6898,11 @@
           <t>網膜</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>中心性漿液性脈絡網膜症</t>
+        </is>
+      </c>
       <c r="H70" t="n">
         <v>5</v>
       </c>
@@ -6929,7 +7000,11 @@
           <t>角膜</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>角膜炎</t>
+        </is>
+      </c>
       <c r="H71" t="n">
         <v>4</v>
       </c>
@@ -7022,7 +7097,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>3</v>
       </c>
@@ -7120,7 +7194,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>4</v>
       </c>
@@ -7218,7 +7291,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>3</v>
       </c>
@@ -7311,7 +7383,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7404,7 +7480,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>遮閉法</t>
+        </is>
+      </c>
       <c r="H76" t="n">
         <v>3</v>
       </c>
@@ -7497,7 +7577,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>1</v>
       </c>
@@ -7589,7 +7668,11 @@
           <t>細胞の構造と機能</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>細胞膜、核、ミトコンドリア</t>
+        </is>
+      </c>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7681,7 +7764,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>3</v>
       </c>
@@ -7773,7 +7855,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>3</v>
       </c>
@@ -7865,7 +7946,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>1</v>
       </c>
@@ -7957,7 +8037,6 @@
           <t>公衆衛生総論</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>2</v>
       </c>
@@ -8049,7 +8128,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>2</v>
       </c>
@@ -8141,7 +8219,6 @@
           <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>3</v>
       </c>
@@ -8233,7 +8310,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>2</v>
       </c>
@@ -8325,7 +8401,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>3</v>
       </c>
@@ -8417,7 +8492,6 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>2</v>
       </c>
@@ -8509,7 +8583,11 @@
           <t>両眼視</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>成立の生理学的機序</t>
+        </is>
+      </c>
       <c r="H88" t="n">
         <v>4</v>
       </c>
@@ -8601,7 +8679,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H89" t="n">
         <v>3</v>
       </c>
@@ -8693,7 +8775,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>1</v>
       </c>
@@ -8785,7 +8866,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H91" t="n">
         <v>4</v>
       </c>
@@ -8883,7 +8968,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>3</v>
       </c>
@@ -8975,7 +9059,6 @@
           <t>屈折異常</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>2</v>
       </c>
@@ -9067,7 +9150,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>4</v>
       </c>
@@ -9160,7 +9242,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H95" t="n">
         <v>3</v>
       </c>
@@ -9253,7 +9339,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>2</v>
       </c>
@@ -9345,7 +9430,6 @@
           <t>ロービジョン</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>2</v>
       </c>
@@ -9439,7 +9523,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>2</v>
       </c>
@@ -9531,7 +9614,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>2</v>
       </c>
@@ -9623,7 +9705,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>3</v>
       </c>
@@ -9715,7 +9796,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>2</v>
       </c>
@@ -9807,7 +9887,6 @@
           <t>眼球</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>2</v>
       </c>
@@ -9899,7 +9978,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>2</v>
       </c>
@@ -9991,7 +10069,11 @@
           <t>瞳孔反応</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>対光反射</t>
+        </is>
+      </c>
       <c r="H104" t="n">
         <v>2</v>
       </c>
@@ -10083,7 +10165,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>2</v>
       </c>
@@ -10175,7 +10256,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>視神経炎</t>
+        </is>
+      </c>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10267,7 +10352,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>3</v>
       </c>
@@ -10359,7 +10443,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>プリズム</t>
+        </is>
+      </c>
       <c r="H108" t="n">
         <v>3</v>
       </c>
@@ -10452,7 +10540,11 @@
           <t>光学的視能矯正</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>プリズム</t>
+        </is>
+      </c>
       <c r="H109" t="n">
         <v>3</v>
       </c>
@@ -10544,7 +10636,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>3</v>
       </c>
@@ -10637,7 +10728,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>3</v>
       </c>
@@ -10729,7 +10819,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H112" t="n">
         <v>3</v>
       </c>
@@ -10816,7 +10910,11 @@
           <t>前眼部、透光体検査</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>細隙灯顕微鏡検査</t>
+        </is>
+      </c>
       <c r="H113" t="n">
         <v>3</v>
       </c>
@@ -10914,7 +11012,11 @@
           <t>水晶体</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>白内障</t>
+        </is>
+      </c>
       <c r="H114" t="n">
         <v>2</v>
       </c>
@@ -11006,7 +11108,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>1</v>
       </c>
@@ -11098,7 +11199,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>視神経症</t>
+        </is>
+      </c>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11190,7 +11295,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>4</v>
       </c>
@@ -11282,7 +11386,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>眼鏡レンズ</t>
+        </is>
+      </c>
       <c r="H118" t="n">
         <v>4</v>
       </c>
@@ -11375,7 +11483,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>3</v>
       </c>
@@ -11467,7 +11574,6 @@
           <t>全身疾患と眼</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>2</v>
       </c>
@@ -11559,7 +11665,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H121" t="n">
         <v>2</v>
       </c>
@@ -11651,7 +11761,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>3</v>
       </c>
@@ -11743,7 +11852,11 @@
           <t>網膜</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>糖尿病網膜症</t>
+        </is>
+      </c>
       <c r="H123" t="n">
         <v>2</v>
       </c>
@@ -11835,7 +11948,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H124" t="n">
         <v>3</v>
       </c>
@@ -11927,7 +12044,11 @@
           <t>硝子体</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>硝子体出血、混濁、後部硝子体剥離</t>
+        </is>
+      </c>
       <c r="H125" t="n">
         <v>1</v>
       </c>
@@ -12019,7 +12140,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>4</v>
       </c>
@@ -12111,7 +12231,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>2</v>
       </c>
@@ -12203,7 +12322,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>2</v>
       </c>
@@ -12295,7 +12413,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>3</v>
       </c>
@@ -12387,7 +12504,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>3</v>
       </c>
@@ -12479,7 +12595,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H131" t="n">
         <v>3</v>
       </c>
@@ -12571,7 +12691,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H132" t="n">
         <v>2</v>
       </c>
@@ -12663,7 +12787,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>単眼運動とその法則</t>
+        </is>
+      </c>
       <c r="H133" t="n">
         <v>2</v>
       </c>
@@ -12755,7 +12883,11 @@
           <t>両眼視</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>静的立体視と動的立体視</t>
+        </is>
+      </c>
       <c r="H134" t="n">
         <v>2</v>
       </c>
@@ -12847,7 +12979,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>測定法</t>
+        </is>
+      </c>
       <c r="H135" t="n">
         <v>3</v>
       </c>
@@ -12940,7 +13076,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>2</v>
       </c>
@@ -13032,7 +13167,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>3</v>
       </c>
@@ -13130,7 +13264,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H138" t="n">
         <v>3</v>
       </c>
@@ -13222,7 +13360,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>不同視弱視</t>
+        </is>
+      </c>
       <c r="H139" t="n">
         <v>3</v>
       </c>
@@ -13315,7 +13457,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>微小斜視弱視</t>
+        </is>
+      </c>
       <c r="H140" t="n">
         <v>3</v>
       </c>
@@ -13407,7 +13553,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H141" t="n">
         <v>3</v>
       </c>
@@ -13499,7 +13649,6 @@
           <t>眼瞼</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>4</v>
       </c>
@@ -13597,7 +13746,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>老視</t>
+        </is>
+      </c>
       <c r="H143" t="n">
         <v>3</v>
       </c>
@@ -13690,7 +13843,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>4</v>
       </c>
@@ -13788,7 +13940,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>3</v>
       </c>
@@ -13881,7 +14032,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>3</v>
       </c>
@@ -13974,7 +14124,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H147" t="n">
         <v>4</v>
       </c>
@@ -14072,7 +14226,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H148" t="n">
         <v>4</v>
       </c>
@@ -14165,7 +14323,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>4</v>
       </c>
@@ -14263,7 +14420,11 @@
           <t>光学的視能矯正</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>プリズム</t>
+        </is>
+      </c>
       <c r="H150" t="n">
         <v>3</v>
       </c>
@@ -14356,7 +14517,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
         <v>3</v>
       </c>

--- a/CO国試data/CO_questions_2018.xlsx
+++ b/CO国試data/CO_questions_2018.xlsx
@@ -603,10 +603,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S2" t="b">
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -699,10 +697,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S3" t="b">
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,10 +882,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S5" t="b">
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -982,10 +976,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S6" t="b">
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1073,10 +1065,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S7" t="b">
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1164,10 +1154,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S8" t="b">
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1255,10 +1243,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S9" t="b">
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1346,10 +1332,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S10" t="b">
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1437,10 +1421,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S11" t="b">
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1528,10 +1510,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S12" t="b">
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1619,10 +1599,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S13" t="b">
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1710,10 +1688,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S14" t="b">
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1806,10 +1782,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S15" t="b">
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1897,10 +1871,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S16" t="b">
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1988,10 +1960,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S17" t="b">
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2084,10 +2054,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S18" t="b">
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2175,10 +2143,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S19" t="b">
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2271,10 +2237,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S20" t="b">
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2367,10 +2331,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S21" t="b">
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2458,10 +2420,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S22" t="b">
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2549,10 +2509,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S23" t="b">
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2640,10 +2598,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S24" t="b">
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2731,10 +2687,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S25" t="b">
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2827,10 +2781,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S26" t="b">
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2924,10 +2876,8 @@
           <t>2018_co_18_am026.jpg</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S27" t="b">
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3015,10 +2965,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S28" t="b">
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3112,10 +3060,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S29" t="b">
+        <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3294,10 +3240,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S31" t="b">
+        <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3486,10 +3430,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S33" t="b">
+        <v>0</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3582,10 +3524,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S34" t="b">
+        <v>0</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3674,10 +3614,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S35" t="b">
+        <v>0</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3765,10 +3703,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S36" t="b">
+        <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3856,10 +3792,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S37" t="b">
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3952,10 +3886,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S38" t="b">
+        <v>0</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4048,10 +3980,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S39" t="b">
+        <v>0</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4139,10 +4069,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S40" t="b">
+        <v>0</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4230,10 +4158,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S41" t="b">
+        <v>0</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4321,10 +4247,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S42" t="b">
+        <v>0</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4417,10 +4341,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S43" t="b">
+        <v>0</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4513,10 +4435,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S44" t="b">
+        <v>0</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4604,10 +4524,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S45" t="b">
+        <v>0</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4700,10 +4618,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S46" t="b">
+        <v>0</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4796,10 +4712,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S47" t="b">
+        <v>0</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4978,10 +4892,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S49" t="b">
+        <v>0</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5074,10 +4986,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S50" t="b">
+        <v>0</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5170,10 +5080,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S51" t="b">
+        <v>0</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5261,10 +5169,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S52" t="b">
+        <v>0</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5352,10 +5258,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S53" t="b">
+        <v>0</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5448,10 +5352,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S54" t="b">
+        <v>0</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5630,10 +5532,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S56" t="b">
+        <v>0</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5726,10 +5626,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S57" t="b">
+        <v>0</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5817,10 +5715,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S58" t="b">
+        <v>0</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5999,10 +5895,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S60" t="b">
+        <v>0</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6095,10 +5989,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S61" t="b">
+        <v>0</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6191,10 +6083,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S62" t="b">
+        <v>0</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6282,10 +6172,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S63" t="b">
+        <v>0</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6379,10 +6267,8 @@
           <t>2018_co_18_am063.jpg</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S64" t="b">
+        <v>0</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6475,10 +6361,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S65" t="b">
+        <v>0</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6668,10 +6552,8 @@
           <t>2018_co_18_am066.jpg</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S67" t="b">
+        <v>0</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6855,10 +6737,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S69" t="b">
+        <v>0</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6957,10 +6837,8 @@
           <t>2018_co_18_am069.jpg</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S70" t="b">
+        <v>0</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7054,10 +6932,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S71" t="b">
+        <v>0</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7248,10 +7124,8 @@
           <t>2018_co_18_am072.jpg</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S73" t="b">
+        <v>0</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7340,10 +7214,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S74" t="b">
+        <v>0</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7437,10 +7309,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S75" t="b">
+        <v>0</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7534,10 +7404,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S76" t="b">
+        <v>0</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7625,10 +7493,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S77" t="b">
+        <v>0</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7721,10 +7587,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S78" t="b">
+        <v>0</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -7812,10 +7676,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S79" t="b">
+        <v>0</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -7903,10 +7765,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S80" t="b">
+        <v>0</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -7994,10 +7854,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S81" t="b">
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8085,10 +7943,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S82" t="b">
+        <v>0</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8176,10 +8032,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S83" t="b">
+        <v>0</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8358,10 +8212,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S85" t="b">
+        <v>0</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8449,10 +8301,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S86" t="b">
+        <v>0</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8540,10 +8390,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S87" t="b">
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8823,10 +8671,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S90" t="b">
+        <v>0</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -8925,10 +8771,8 @@
           <t>2018_co_18_pm015.jpg</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S91" t="b">
+        <v>0</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9016,10 +8860,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S92" t="b">
+        <v>0</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9107,10 +8949,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S93" t="b">
+        <v>0</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9199,10 +9039,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S94" t="b">
+        <v>0</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9296,10 +9134,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S95" t="b">
+        <v>0</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9387,10 +9223,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S96" t="b">
+        <v>0</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9480,10 +9314,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S97" t="b">
+        <v>0</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -9571,10 +9403,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S98" t="b">
+        <v>0</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -9662,10 +9492,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S99" t="b">
+        <v>0</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -9844,10 +9672,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S101" t="b">
+        <v>0</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -9935,10 +9761,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S102" t="b">
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10026,10 +9850,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S103" t="b">
+        <v>0</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10122,10 +9944,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S104" t="b">
+        <v>0</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10213,10 +10033,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S105" t="b">
+        <v>0</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10309,10 +10127,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S106" t="b">
+        <v>0</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10497,10 +10313,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S108" t="b">
+        <v>0</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -10593,10 +10407,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S109" t="b">
+        <v>0</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -10969,10 +10781,8 @@
           <t>2018_co_18_pm037.jpg</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S113" t="b">
+        <v>0</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11065,10 +10875,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S114" t="b">
+        <v>0</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11156,10 +10964,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S115" t="b">
+        <v>0</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11252,10 +11058,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S116" t="b">
+        <v>0</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11343,10 +11147,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S117" t="b">
+        <v>0</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11440,10 +11242,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S118" t="b">
+        <v>0</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -11531,10 +11331,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S119" t="b">
+        <v>0</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -11622,10 +11420,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S120" t="b">
+        <v>0</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -11718,10 +11514,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S121" t="b">
+        <v>0</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -11809,10 +11603,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S122" t="b">
+        <v>0</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -11905,10 +11697,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S123" t="b">
+        <v>0</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12001,10 +11791,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S124" t="b">
+        <v>0</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12097,10 +11885,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S125" t="b">
+        <v>0</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12279,10 +12065,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S127" t="b">
+        <v>0</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -12370,10 +12154,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S128" t="b">
+        <v>0</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -12461,10 +12243,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S129" t="b">
+        <v>0</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -12552,10 +12332,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S130" t="b">
+        <v>0</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -12648,10 +12426,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S131" t="b">
+        <v>0</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -12744,10 +12520,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S132" t="b">
+        <v>0</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -12840,10 +12614,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S133" t="b">
+        <v>0</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -12936,10 +12708,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S134" t="b">
+        <v>0</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13033,10 +12803,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S135" t="b">
+        <v>0</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13124,10 +12892,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S136" t="b">
+        <v>0</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13221,10 +12987,8 @@
           <t>2018_co_18_pm061.jpg</t>
         </is>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S137" t="b">
+        <v>0</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -13317,10 +13081,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S138" t="b">
+        <v>0</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -13414,10 +13176,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S139" t="b">
+        <v>0</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -13510,10 +13270,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S140" t="b">
+        <v>0</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -13606,10 +13364,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S141" t="b">
+        <v>0</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -13703,10 +13459,8 @@
           <t>2018_co_18_pm066.jpg</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S142" t="b">
+        <v>0</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -13800,10 +13554,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S143" t="b">
+        <v>0</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -13897,10 +13649,8 @@
           <t>2018_co_18_pm068.jpg</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S144" t="b">
+        <v>0</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -13989,10 +13739,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S145" t="b">
+        <v>0</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -14081,10 +13829,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S146" t="b">
+        <v>0</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -14183,10 +13929,8 @@
           <t>2018_co_18_pm071.jpg</t>
         </is>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S147" t="b">
+        <v>0</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -14377,10 +14121,8 @@
           <t>2018_co_18_pm073.jpg</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S149" t="b">
+        <v>0</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -14566,10 +14308,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S151" t="b">
+        <v>0</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>

--- a/CO国試data/CO_questions_2018.xlsx
+++ b/CO国試data/CO_questions_2018.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -791,10 +791,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S4" t="b">
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3136,7 +3134,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3149,10 +3147,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S30" t="b">
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3321,7 +3317,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3334,10 +3330,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S32" t="b">
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4788,7 +4782,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4801,10 +4795,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S48" t="b">
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5428,7 +5420,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5441,10 +5433,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S55" t="b">
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5791,7 +5781,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5804,10 +5794,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S59" t="b">
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6437,7 +6425,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6450,10 +6438,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S66" t="b">
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6628,7 +6614,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6646,10 +6632,8 @@
           <t>2018_co_18_am067.jpg</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S68" t="b">
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7009,7 +6993,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -7027,10 +7011,8 @@
           <t>2018_co_18_am071.jpg</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S72" t="b">
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8108,7 +8090,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -8121,10 +8103,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S84" t="b">
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8471,7 +8451,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -8484,10 +8464,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S88" t="b">
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -8567,7 +8545,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -8580,10 +8558,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S89" t="b">
+        <v>1</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9568,7 +9544,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -9581,10 +9557,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S100" t="b">
+        <v>1</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10203,7 +10177,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -10216,10 +10190,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S107" t="b">
+        <v>1</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -10484,7 +10456,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -10497,10 +10469,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S110" t="b">
+        <v>1</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -10575,7 +10545,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -10588,10 +10558,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S111" t="b">
+        <v>1</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11961,7 +11929,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -11974,10 +11942,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S126" t="b">
+        <v>1</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14011,7 +13977,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -14024,10 +13990,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S148" t="b">
+        <v>1</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -14203,7 +14167,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -14216,10 +14180,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S150" t="b">
+        <v>1</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
